--- a/artfynd/A 7125-2023 artfynd.xlsx
+++ b/artfynd/A 7125-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7125-2023 artfynd.xlsx
+++ b/artfynd/A 7125-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93017011</v>
+        <v>113245835</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668192.6820228165</v>
+        <v>668079</v>
       </c>
       <c r="R2" t="n">
-        <v>6706215.596838974</v>
+        <v>6706300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104502051</v>
+        <v>113245836</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utmossarna, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667777.0084357379</v>
+        <v>668160</v>
       </c>
       <c r="R3" t="n">
-        <v>6705639.49024437</v>
+        <v>6706252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108409864</v>
+        <v>113245837</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667916.970684969</v>
+        <v>668181</v>
       </c>
       <c r="R4" t="n">
-        <v>6706185.500321371</v>
+        <v>6706276</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108409865</v>
+        <v>113245841</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668019.0148812898</v>
+        <v>668140</v>
       </c>
       <c r="R5" t="n">
-        <v>6706300.404187184</v>
+        <v>6706336</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1063,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108415217</v>
+        <v>113246108</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668022.3899518341</v>
+        <v>668260</v>
       </c>
       <c r="R6" t="n">
-        <v>6705918.667866307</v>
+        <v>6706080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1164,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108409863</v>
+        <v>113246115</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667866.926955002</v>
+        <v>668279</v>
       </c>
       <c r="R7" t="n">
-        <v>6706122.906379519</v>
+        <v>6706304</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1265,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108409861</v>
+        <v>104502074</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1292,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Utmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>667904.3645433345</v>
+        <v>667793</v>
       </c>
       <c r="R8" t="n">
-        <v>6706073.263237373</v>
+        <v>6705644</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1355,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,62 +1375,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108415215</v>
+        <v>113245844</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>667828.6973412224</v>
+        <v>667966</v>
       </c>
       <c r="R9" t="n">
-        <v>6705837.545477262</v>
+        <v>6706437</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1452,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,62 +1472,66 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108415213</v>
+        <v>93017009</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>667895.4154862339</v>
+        <v>668165</v>
       </c>
       <c r="R10" t="n">
-        <v>6705754.176168767</v>
+        <v>6706271</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1558,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1578,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108415216</v>
+        <v>92557847</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1601,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667957.8018051866</v>
+        <v>668227</v>
       </c>
       <c r="R11" t="n">
-        <v>6705902.823783731</v>
+        <v>6706460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1660,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1680,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108409859</v>
+        <v>92557848</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,37 +1703,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668020.5292980114</v>
+        <v>668222</v>
       </c>
       <c r="R12" t="n">
-        <v>6705990.714396542</v>
+        <v>6706419</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1762,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,27 +1782,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108409860</v>
+        <v>92557849</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,37 +1805,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>667995.3756995556</v>
+        <v>668248</v>
       </c>
       <c r="R13" t="n">
-        <v>6706106.141902547</v>
+        <v>6706413</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,22 +1864,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,27 +1884,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108409866</v>
+        <v>108415152</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,37 +1907,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668005.0717969275</v>
+        <v>668117</v>
       </c>
       <c r="R14" t="n">
-        <v>6706430.1741502</v>
+        <v>6705729</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,19 +1972,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,27 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108415214</v>
+        <v>108424218</v>
       </c>
       <c r="B15" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,37 +2012,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814.2896270491</v>
+        <v>668158</v>
       </c>
       <c r="R15" t="n">
-        <v>6705753.377855701</v>
+        <v>6706319</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,19 +2077,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,27 +2094,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108424257</v>
+        <v>108409830</v>
       </c>
       <c r="B16" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2117,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668194.2749181653</v>
+        <v>668085</v>
       </c>
       <c r="R16" t="n">
-        <v>6706074.870091319</v>
+        <v>6705720</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2316,19 +2174,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,27 +2191,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108424267</v>
+        <v>113245839</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,37 +2214,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668220.9406347397</v>
+        <v>668176</v>
       </c>
       <c r="R17" t="n">
-        <v>6706703.990175959</v>
+        <v>6706311</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,22 +2268,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,27 +2288,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108424263</v>
+        <v>113245843</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,37 +2315,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668187.3429377358</v>
+        <v>668054</v>
       </c>
       <c r="R18" t="n">
-        <v>6706330.455436424</v>
+        <v>6706372</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2537,22 +2369,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,27 +2389,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108424261</v>
+        <v>87141595</v>
       </c>
       <c r="B19" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,37 +2416,53 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Utmossarna 1,8 km VSV om Skaten, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668204.3094528762</v>
+        <v>667772</v>
       </c>
       <c r="R19" t="n">
-        <v>6706167.722237788</v>
+        <v>6705764</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,22 +2486,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,33 +2500,38 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>108424265</v>
+        <v>113246116</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,37 +2539,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668059.7783727007</v>
+        <v>668278</v>
       </c>
       <c r="R20" t="n">
-        <v>6706466.800528177</v>
+        <v>6706305</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,22 +2593,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,65 +2613,76 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>108424271</v>
+        <v>87141514</v>
       </c>
       <c r="B21" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Utmossarna 1,8 km VSV om Skaten, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668316.2860935072</v>
+        <v>667745</v>
       </c>
       <c r="R21" t="n">
-        <v>6706760.290776655</v>
+        <v>6705787</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,22 +2706,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Små askplantor.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,68 +2725,81 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Jörgen Sjöström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>108424273</v>
+        <v>108424234</v>
       </c>
       <c r="B22" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668325.2571759088</v>
+        <v>668217</v>
       </c>
       <c r="R22" t="n">
-        <v>6706833.319068645</v>
+        <v>6706697</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2988,27 +2829,18 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3027,53 +2859,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>108424275</v>
+        <v>113246107</v>
       </c>
       <c r="B23" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668362.0782165673</v>
+        <v>668265</v>
       </c>
       <c r="R23" t="n">
-        <v>6706860.717723515</v>
+        <v>6706088</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3097,22 +2924,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,65 +2944,64 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108424269</v>
+        <v>113246117</v>
       </c>
       <c r="B24" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668256.7059479144</v>
+        <v>668292</v>
       </c>
       <c r="R24" t="n">
-        <v>6706711.580985073</v>
+        <v>6706369</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3209,22 +3025,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,65 +3045,64 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>108424259</v>
+        <v>113246118</v>
       </c>
       <c r="B25" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668190.3691114081</v>
+        <v>668287</v>
       </c>
       <c r="R25" t="n">
-        <v>6706169.544405418</v>
+        <v>6706414</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3321,22 +3126,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,73 +3146,64 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>108424234</v>
+        <v>104502051</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Utmossarna, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668216.8181625509</v>
+        <v>667777</v>
       </c>
       <c r="R26" t="n">
-        <v>6706696.883001016</v>
+        <v>6705640</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3441,22 +3227,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,34 +3241,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113245839</v>
+        <v>104502054</v>
       </c>
       <c r="B27" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,34 +3270,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Utmossarna, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668176</v>
+        <v>667777</v>
       </c>
       <c r="R27" t="n">
-        <v>6706311</v>
+        <v>6705616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3554,12 +3324,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,31 +3344,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113245843</v>
+        <v>113245842</v>
       </c>
       <c r="B28" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3630,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668054</v>
+        <v>668099</v>
       </c>
       <c r="R28" t="n">
-        <v>6706372</v>
+        <v>6706346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3696,15 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113245863</v>
+        <v>93017011</v>
       </c>
       <c r="B29" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,14 +3488,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667791</v>
+        <v>668193</v>
       </c>
       <c r="R29" t="n">
-        <v>6705782</v>
+        <v>6706216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,12 +3522,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3786,31 +3542,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113245841</v>
+        <v>108409859</v>
       </c>
       <c r="B30" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3818,37 +3565,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668140</v>
+        <v>668021</v>
       </c>
       <c r="R30" t="n">
-        <v>6706336</v>
+        <v>6705990</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3872,12 +3619,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3892,31 +3639,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113245837</v>
+        <v>108409860</v>
       </c>
       <c r="B31" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3924,37 +3662,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668181</v>
+        <v>667995</v>
       </c>
       <c r="R31" t="n">
-        <v>6706276</v>
+        <v>6706106</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3978,12 +3716,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3998,31 +3736,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113245836</v>
+        <v>108409861</v>
       </c>
       <c r="B32" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,37 +3759,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668160</v>
+        <v>667905</v>
       </c>
       <c r="R32" t="n">
-        <v>6706252</v>
+        <v>6706073</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4084,12 +3813,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4104,15 +3833,2149 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>108409863</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>667867</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6706123</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>108409864</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>667917</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6706185</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>108409865</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>668019</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6706301</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>108409866</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>668005</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6706430</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>108409867</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>668015</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6706515</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>108415213</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>667896</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6705754</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>108415214</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>667815</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6705753</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>108415215</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>667828</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6705837</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>108415216</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>667958</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6705903</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>108415217</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>668023</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6705918</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>108424256</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>668059</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6705946</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>108424257</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>668195</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6706075</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>108424259</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>668190</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6706170</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>108424261</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>668205</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6706168</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>108424263</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>668188</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6706331</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>108424265</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>668060</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6706467</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>108424267</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>668221</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6706704</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>108424269</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>668256</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6706711</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>108424271</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>668316</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6706760</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>108424273</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>668325</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6706833</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>108424275</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>668362</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6706860</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>113245863</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Göksnåre, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>667791</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6705782</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Axel Linder</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Cecilia Rätz, Dennis Nyström</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
+      <c r="AY54" t="inlineStr">
         <is>
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>

--- a/artfynd/A 7125-2023 artfynd.xlsx
+++ b/artfynd/A 7125-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245837</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246115</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104502074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93017009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92557847</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92557848</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92557849</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415152</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424218</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409830</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2301,6 +2381,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245839</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2402,6 +2487,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245843</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87141595</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246116</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2748,6 +2848,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87141514</t>
         </is>
       </c>
     </row>
@@ -2856,6 +2961,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424234</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2957,6 +3067,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246107</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3058,6 +3173,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246117</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3159,6 +3279,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246118</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3256,6 +3381,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104502051</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3353,6 +3483,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104502054</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3454,6 +3589,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245842</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3551,6 +3691,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93017011</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3648,6 +3793,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409859</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3745,6 +3895,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409860</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3842,6 +3997,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409861</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3939,6 +4099,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409863</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4036,6 +4201,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409864</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4133,6 +4303,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409865</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4230,6 +4405,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409866</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4327,6 +4507,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409867</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4424,6 +4609,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415213</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4521,6 +4711,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415214</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4618,6 +4813,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415215</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4715,6 +4915,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415216</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4812,6 +5017,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415217</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4909,6 +5119,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424256</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5006,6 +5221,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424257</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5103,6 +5323,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424259</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5200,6 +5425,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424261</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5297,6 +5527,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424263</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5394,6 +5629,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424265</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5491,6 +5731,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424267</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5588,6 +5833,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424269</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5685,6 +5935,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424271</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5782,6 +6037,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424273</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5879,6 +6139,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424275</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5980,8 +6245,68 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>